--- a/progLinear/exercicios/Simplex_duas_fases_2.xlsx
+++ b/progLinear/exercicios/Simplex_duas_fases_2.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/29ef9a7b83f2ddc4/Arquivo_pessoal/Ensino/programacao-linear/"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="762" documentId="8_{10D4449C-708C-42DB-9081-ACFF8956C39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40A79F1E-124C-40B6-92FE-B924155E133B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F3C3C58E-ED1D-4D2E-BCE5-E3214E2C89B9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{F3C3C58E-ED1D-4D2E-BCE5-E3214E2C89B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Exemplo1-completo" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -114,94 +114,94 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="32">
   <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>Minimizar</t>
+  </si>
+  <si>
+    <t>Decisão</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>Sujeito a</t>
+  </si>
+  <si>
+    <t>Restrições</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>FASE 1</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Coeficientes</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>razão</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>C-W</t>
+  </si>
+  <si>
+    <t>L1'=L1/3</t>
+  </si>
+  <si>
+    <t>L2'=L2-L1</t>
+  </si>
+  <si>
+    <t>INVIÁVEL</t>
+  </si>
+  <si>
     <t>Maximizar</t>
   </si>
   <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>x2</t>
-  </si>
-  <si>
-    <t>Decisão</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>Sujeito a</t>
-  </si>
-  <si>
-    <t>Restrições</t>
-  </si>
-  <si>
-    <t>&lt;=</t>
-  </si>
-  <si>
-    <t>&gt;=</t>
-  </si>
-  <si>
-    <t>Minimizar</t>
-  </si>
-  <si>
-    <t>FASE 1</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Coeficientes</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>C-W</t>
-  </si>
-  <si>
-    <t>razão</t>
-  </si>
-  <si>
-    <t>L1'=L1/3</t>
-  </si>
-  <si>
-    <t>L2'=L2-L1</t>
-  </si>
-  <si>
-    <t>INVIÁVEL</t>
+    <t>=</t>
+  </si>
+  <si>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>FASE 2</t>
+  </si>
+  <si>
+    <t>C-Z</t>
   </si>
   <si>
     <t>x</t>
   </si>
   <si>
     <t>y</t>
-  </si>
-  <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>a1</t>
-  </si>
-  <si>
-    <t>a2</t>
-  </si>
-  <si>
-    <t>FASE 2</t>
-  </si>
-  <si>
-    <t>C-Z</t>
   </si>
   <si>
     <t>variáveis</t>
@@ -214,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,23 +609,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97EF0-FE72-442C-9BD4-1073FF9FEE2F}">
   <dimension ref="A2:M20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -634,7 +634,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -652,17 +652,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>2</v>
       </c>
@@ -676,7 +676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="B8">
         <v>1</v>
       </c>
@@ -690,26 +690,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -718,15 +718,15 @@
         <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11">
       <c r="B12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="B13" t="s">
         <v>14</v>
       </c>
@@ -784,7 +784,7 @@
         <v>3.3333333333333335</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="C14" t="s">
         <v>17</v>
       </c>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="C15" t="s">
         <v>18</v>
       </c>
@@ -830,9 +830,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13">
       <c r="B17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -862,10 +862,10 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="K17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18" s="3" t="s">
         <v>14</v>
       </c>
@@ -897,13 +897,13 @@
         <v>6</v>
       </c>
       <c r="K18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:13">
       <c r="C19" t="s">
         <v>17</v>
       </c>
@@ -932,7 +932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13">
       <c r="C20" t="s">
         <v>18</v>
       </c>
@@ -972,25 +972,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E02A85-E5C4-42D4-BB79-BB69C9176D9C}">
   <dimension ref="A2:L43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="B3">
         <v>1</v>
       </c>
@@ -998,7 +998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1016,12 +1016,12 @@
         <v>26.461538461538467</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="B8">
         <v>2</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <f>SUMPRODUCT(B4:C4,B8:C8)</f>
@@ -1057,7 +1057,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="B9">
         <v>4</v>
       </c>
@@ -1075,44 +1075,44 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" s="5" customFormat="1">
       <c r="A12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="L12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:12" s="5" customFormat="1">
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -1143,9 +1143,9 @@
         <v>3.3333333333333335</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" s="5" customFormat="1">
       <c r="B14" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -1176,9 +1176,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" s="5" customFormat="1">
       <c r="B15" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" s="5" customFormat="1">
       <c r="C16" s="5" t="s">
         <v>17</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" s="5" customFormat="1">
       <c r="C17" s="5" t="s">
         <v>18</v>
       </c>
@@ -1261,42 +1261,42 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" s="5" customFormat="1"/>
+    <row r="19" spans="2:12">
       <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="L19" t="s">
         <v>16</v>
       </c>
-      <c r="L19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:12">
       <c r="B20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>9</v>
@@ -1334,9 +1334,9 @@
         <v>-5.0000000000000009</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12">
       <c r="B21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1374,9 +1374,9 @@
         <v>6.3076923076923075</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12">
       <c r="B22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>19.428571428571431</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12">
       <c r="C23" t="s">
         <v>17</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12">
       <c r="C24" t="s">
         <v>18</v>
       </c>
@@ -1480,38 +1480,38 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12">
       <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="D26" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="2:12">
       <c r="B27" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>9</v>
@@ -1544,9 +1544,9 @@
         <v>7.5384618829586074</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12">
       <c r="B28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1579,9 +1579,9 @@
         <v>6.307692792899446</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12">
       <c r="B29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>61.230767386982109</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12">
       <c r="C30" t="s">
         <v>17</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>86.769235325325809</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12">
       <c r="C31" t="s">
         <v>18</v>
       </c>
@@ -1680,35 +1680,35 @@
         <v>61.230764674674191</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:8">
       <c r="B34" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1729,9 +1729,9 @@
         <v>7.5384618829586074</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="B35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -1752,9 +1752,9 @@
         <v>6.307692792899446</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="B36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>61.230767386982109</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="C37" t="s">
         <v>4</v>
       </c>
@@ -1800,9 +1800,9 @@
         <v>26.461540261656946</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="C38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D38">
         <f>1-D37</f>
@@ -1821,31 +1821,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="B40" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40">
         <v>7.54</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="B41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
         <v>6.3</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="B42" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C42">
         <v>61.2</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="B43" t="s">
         <v>4</v>
       </c>
@@ -1861,23 +1861,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1164D77C-6F5E-4652-A88E-ECC22BA3A9E6}">
   <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="13.21875" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="B1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -1886,7 +1886,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1904,12 +1904,12 @@
         <v>36.000000000000014</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="B6">
         <v>3</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="B7">
         <v>4</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <f>SUMPRODUCT(B3:C3,B7:C7)</f>
@@ -1945,41 +1945,41 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
         <v>16</v>
       </c>
-      <c r="K9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11">
       <c r="B10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2007,9 +2007,9 @@
         <v>6.666666666666667</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="B11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="C12" t="s">
         <v>17</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11">
       <c r="C13" t="s">
         <v>31</v>
       </c>
@@ -2083,39 +2083,39 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11">
       <c r="B15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="D15" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="B16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -2149,9 +2149,9 @@
         <v>10.000000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="B17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>3.9999999999999987</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="C18" t="s">
         <v>17</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>46.666666666666671</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="C19" t="s">
         <v>18</v>
       </c>
@@ -2243,39 +2243,39 @@
         <v>5.3333333333333286</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="B21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="D21" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="B22" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -2303,9 +2303,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="B23" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -2334,7 +2334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="C24" t="s">
         <v>17</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="C25" t="s">
         <v>18</v>
       </c>
@@ -2390,29 +2390,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="B28" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -2427,9 +2427,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11">
       <c r="B29" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2444,7 +2444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11">
       <c r="C30" t="s">
         <v>4</v>
       </c>
@@ -2460,9 +2460,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="C31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D31">
         <v>0</v>
